--- a/artfynd/A 7083-2025 artfynd.xlsx
+++ b/artfynd/A 7083-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269742</v>
       </c>
       <c r="B2" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137269741</v>
       </c>
       <c r="B3" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137269752</v>
       </c>
       <c r="B4" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>137269753</v>
       </c>
       <c r="B5" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137269754</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137269746</v>
       </c>
       <c r="B7" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137269744</v>
       </c>
       <c r="B8" t="n">
-        <v>98473</v>
+        <v>98483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7083-2025 artfynd.xlsx
+++ b/artfynd/A 7083-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269742</v>
       </c>
       <c r="B2" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137269741</v>
       </c>
       <c r="B3" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137269744</v>
       </c>
       <c r="B8" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7083-2025 artfynd.xlsx
+++ b/artfynd/A 7083-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269742</v>
       </c>
       <c r="B2" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137269741</v>
       </c>
       <c r="B3" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137269752</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>137269753</v>
       </c>
       <c r="B5" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137269754</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137269746</v>
       </c>
       <c r="B7" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137269744</v>
       </c>
       <c r="B8" t="n">
-        <v>98484</v>
+        <v>98489</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7083-2025 artfynd.xlsx
+++ b/artfynd/A 7083-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269742</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137269741</v>
       </c>
       <c r="B3" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137269744</v>
       </c>
       <c r="B8" t="n">
-        <v>98489</v>
+        <v>98491</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7083-2025 artfynd.xlsx
+++ b/artfynd/A 7083-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269742</v>
       </c>
       <c r="B2" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137269741</v>
       </c>
       <c r="B3" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137269752</v>
       </c>
       <c r="B4" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>137269753</v>
       </c>
       <c r="B5" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137269754</v>
       </c>
       <c r="B6" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137269746</v>
       </c>
       <c r="B7" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137269744</v>
       </c>
       <c r="B8" t="n">
-        <v>98491</v>
+        <v>98497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7083-2025 artfynd.xlsx
+++ b/artfynd/A 7083-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269742</v>
       </c>
       <c r="B2" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137269741</v>
       </c>
       <c r="B3" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137269744</v>
       </c>
       <c r="B8" t="n">
-        <v>98497</v>
+        <v>98509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7083-2025 artfynd.xlsx
+++ b/artfynd/A 7083-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269742</v>
       </c>
       <c r="B2" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137269741</v>
       </c>
       <c r="B3" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137269744</v>
       </c>
       <c r="B8" t="n">
-        <v>98509</v>
+        <v>98510</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7083-2025 artfynd.xlsx
+++ b/artfynd/A 7083-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269742</v>
       </c>
       <c r="B2" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137269741</v>
       </c>
       <c r="B3" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137269744</v>
       </c>
       <c r="B8" t="n">
-        <v>98510</v>
+        <v>98513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7083-2025 artfynd.xlsx
+++ b/artfynd/A 7083-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269742</v>
       </c>
       <c r="B2" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137269741</v>
       </c>
       <c r="B3" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137269752</v>
       </c>
       <c r="B4" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>137269753</v>
       </c>
       <c r="B5" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137269754</v>
       </c>
       <c r="B6" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137269746</v>
       </c>
       <c r="B7" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137269744</v>
       </c>
       <c r="B8" t="n">
-        <v>98513</v>
+        <v>98517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
